--- a/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,45</t>
+          <t>1,06; 3,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,55</t>
+          <t>2,55; 5,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,55</t>
+          <t>2,62; 5,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,83</t>
+          <t>2,75; 6,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,64</t>
+          <t>3,4; 6,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,8</t>
+          <t>3,4; 6,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,54</t>
+          <t>9,77; 14,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,0</t>
+          <t>2,58; 5,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,6</t>
+          <t>2,56; 4,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,64</t>
+          <t>3,38; 5,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,43</t>
+          <t>6,58; 9,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,99</t>
+          <t>2,98; 4,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,38</t>
+          <t>2,15; 4,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,32</t>
+          <t>1,52; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,55</t>
+          <t>3,06; 5,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,59</t>
+          <t>1,18; 3,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,23</t>
+          <t>3,42; 6,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,86</t>
+          <t>3,85; 6,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,16</t>
+          <t>7,46; 11,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,32</t>
+          <t>4,08; 6,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,84</t>
+          <t>3,08; 4,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,7</t>
+          <t>2,95; 4,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,94</t>
+          <t>5,67; 7,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,47</t>
+          <t>2,35; 4,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,16</t>
+          <t>2,33; 5,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,79</t>
+          <t>1,29; 3,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,17</t>
+          <t>3,06; 6,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,87</t>
+          <t>2,22; 5,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,5</t>
+          <t>3,47; 6,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,36</t>
+          <t>3,49; 6,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,86</t>
+          <t>8,32; 12,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 58,18</t>
+          <t>4,36; 61,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,39</t>
+          <t>3,32; 5,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,57</t>
+          <t>2,63; 4,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,82</t>
+          <t>6,18; 8,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 43,65</t>
+          <t>3,79; 43,04</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,51</t>
+          <t>1,63; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,67</t>
+          <t>2,92; 5,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,12</t>
+          <t>4,15; 7,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,75</t>
+          <t>2,6; 5,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,7</t>
+          <t>3,08; 5,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,38</t>
+          <t>3,55; 6,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,1</t>
+          <t>10,53; 15,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,33</t>
+          <t>3,27; 5,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,25</t>
+          <t>2,56; 4,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,61</t>
+          <t>3,61; 5,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 10,72</t>
+          <t>7,98; 10,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,13</t>
+          <t>3,39; 5,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,4</t>
+          <t>2,25; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,66</t>
+          <t>2,55; 3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,28</t>
+          <t>3,81; 5,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,1</t>
+          <t>2,39; 3,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,36</t>
+          <t>3,93; 5,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,83</t>
+          <t>4,23; 5,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 12,16</t>
+          <t>9,92; 12,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 26,62</t>
+          <t>4,35; 26,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,19</t>
+          <t>3,27; 4,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,51</t>
+          <t>3,59; 4,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,52</t>
+          <t>7,25; 8,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 16,58</t>
+          <t>3,78; 15,79</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7933; 23912</t>
+          <t>7327; 23138</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17809; 39062</t>
+          <t>17942; 39525</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17172; 37456</t>
+          <t>17706; 38486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17274; 37037</t>
+          <t>17470; 38390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23322; 45692</t>
+          <t>23385; 45853</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24742; 47412</t>
+          <t>23689; 46157</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63396; 97802</t>
+          <t>65738; 99035</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19111; 36249</t>
+          <t>18702; 36852</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36143; 63548</t>
+          <t>35357; 60633</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46354; 78946</t>
+          <t>47344; 77330</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88332; 127041</t>
+          <t>88644; 127625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40084; 67843</t>
+          <t>40601; 66213</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19245; 42150</t>
+          <t>20676; 42125</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14608; 33758</t>
+          <t>15493; 34115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30402; 56728</t>
+          <t>31276; 55890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13808; 42872</t>
+          <t>14018; 41757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33120; 60297</t>
+          <t>33151; 59478</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40882; 70844</t>
+          <t>39741; 70349</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77508; 116405</t>
+          <t>77773; 116519</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38551; 60586</t>
+          <t>39107; 61125</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57734; 93412</t>
+          <t>59361; 92477</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59663; 96430</t>
+          <t>60462; 98359</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116537; 164047</t>
+          <t>117005; 162525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54077; 96120</t>
+          <t>50635; 95137</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16262; 35000</t>
+          <t>15791; 35953</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9790; 28686</t>
+          <t>9783; 29187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23438; 46858</t>
+          <t>23214; 46890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14632; 34312</t>
+          <t>15642; 35871</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22863; 44470</t>
+          <t>23705; 46020</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25803; 49405</t>
+          <t>27142; 50270</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64393; 100991</t>
+          <t>65302; 99355</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40098; 543040</t>
+          <t>40732; 576943</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44401; 73487</t>
+          <t>45198; 75255</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40094; 70092</t>
+          <t>40411; 70257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94145; 136288</t>
+          <t>95470; 136077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62649; 715006</t>
+          <t>62066; 705072</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15369; 33073</t>
+          <t>15348; 33992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28413; 53711</t>
+          <t>27652; 53814</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38377; 66745</t>
+          <t>38877; 68096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24503; 53251</t>
+          <t>24143; 53624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32834; 59166</t>
+          <t>31991; 59902</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37521; 67160</t>
+          <t>37327; 65449</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>111346; 157595</t>
+          <t>109920; 158543</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35913; 58340</t>
+          <t>35782; 59599</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51603; 84211</t>
+          <t>50764; 81536</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73206; 112189</t>
+          <t>72275; 111072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>156103; 212407</t>
+          <t>158051; 210797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67200; 103753</t>
+          <t>68470; 104653</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72645; 111320</t>
+          <t>73626; 110999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84953; 125556</t>
+          <t>87233; 129412</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130162; 179186</t>
+          <t>129217; 177646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88845; 141740</t>
+          <t>82858; 137277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>129417; 181201</t>
+          <t>132695; 182661</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>152205; 207429</t>
+          <t>150646; 204182</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>354888; 430916</t>
+          <t>351692; 431385</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>161276; 988032</t>
+          <t>161437; 979354</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>216538; 278899</t>
+          <t>217358; 277457</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>247516; 314833</t>
+          <t>250421; 316364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>495007; 591483</t>
+          <t>502869; 592778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>268313; 1189282</t>
+          <t>271451; 1132535</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,33</t>
+          <t>1,23; 3,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,62</t>
+          <t>2,55; 5,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,7</t>
+          <t>2,72; 5,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,04</t>
+          <t>2,83; 6,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,66</t>
+          <t>3,38; 6,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,62</t>
+          <t>3,49; 6,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,72</t>
+          <t>9,42; 14,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,08</t>
+          <t>2,85; 5,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,39</t>
+          <t>2,54; 4,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,52</t>
+          <t>3,37; 5,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 9,47</t>
+          <t>6,5; 9,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,87</t>
+          <t>3,27; 5,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,38</t>
+          <t>2,08; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,35</t>
+          <t>1,43; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,47</t>
+          <t>2,96; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,5</t>
+          <t>1,81; 4,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,14</t>
+          <t>3,33; 6,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,82</t>
+          <t>3,99; 6,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,17</t>
+          <t>7,51; 11,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,38</t>
+          <t>4,06; 6,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,79</t>
+          <t>3,01; 4,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,8</t>
+          <t>2,96; 4,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,87</t>
+          <t>5,55; 7,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,42</t>
+          <t>3,21; 4,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,3</t>
+          <t>2,41; 5,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,85</t>
+          <t>1,31; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,17</t>
+          <t>2,96; 6,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,09</t>
+          <t>2,28; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,73</t>
+          <t>3,31; 6,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,47</t>
+          <t>3,27; 6,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 12,66</t>
+          <t>8,4; 12,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 61,81</t>
+          <t>3,99; 6,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,52</t>
+          <t>3,26; 5,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,58</t>
+          <t>2,59; 4,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,81</t>
+          <t>6,09; 8,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 43,04</t>
+          <t>3,47; 5,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,61</t>
+          <t>1,53; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,68</t>
+          <t>2,86; 5,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,26</t>
+          <t>4,09; 7,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,79</t>
+          <t>2,53; 5,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,77</t>
+          <t>3,11; 5,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,22</t>
+          <t>3,62; 6,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,19</t>
+          <t>10,66; 15,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,44</t>
+          <t>3,87; 5,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,12</t>
+          <t>2,6; 4,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,55</t>
+          <t>3,58; 5,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 10,64</t>
+          <t>8,06; 10,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,18</t>
+          <t>3,49; 5,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,39</t>
+          <t>2,26; 3,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,78</t>
+          <t>2,48; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,23</t>
+          <t>3,85; 5,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,97</t>
+          <t>2,88; 4,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,41</t>
+          <t>3,85; 5,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,74</t>
+          <t>4,31; 5,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,17</t>
+          <t>9,96; 12,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 26,38</t>
+          <t>4,22; 5,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,17</t>
+          <t>3,24; 4,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 4,53</t>
+          <t>3,53; 4,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,54</t>
+          <t>7,22; 8,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 15,79</t>
+          <t>3,75; 4,63</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25522</t>
+          <t>29330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52624</t>
+          <t>58673</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7327; 23138</t>
+          <t>8525; 24375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17942; 39525</t>
+          <t>17954; 37683</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17706; 38486</t>
+          <t>18356; 38087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17470; 38390</t>
+          <t>19555; 41715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23385; 45853</t>
+          <t>23246; 45593</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23689; 46157</t>
+          <t>24350; 46442</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65738; 99035</t>
+          <t>63388; 97621</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18702; 36852</t>
+          <t>20893; 40375</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35357; 60633</t>
+          <t>35066; 62237</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47344; 77330</t>
+          <t>47142; 79379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88644; 127625</t>
+          <t>87632; 128089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40601; 66213</t>
+          <t>46629; 75645</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49096</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76271</t>
+          <t>83586</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20676; 42125</t>
+          <t>20022; 41729</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15493; 34115</t>
+          <t>14543; 34415</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31276; 55890</t>
+          <t>30277; 56024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14018; 41757</t>
+          <t>19016; 42588</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33151; 59478</t>
+          <t>32235; 58949</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39741; 70349</t>
+          <t>41190; 70680</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77773; 116519</t>
+          <t>78319; 116298</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39107; 61125</t>
+          <t>43515; 68209</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59361; 92477</t>
+          <t>58040; 92860</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60462; 98359</t>
+          <t>60596; 95145</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117005; 162525</t>
+          <t>114524; 163118</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50635; 95137</t>
+          <t>68078; 102863</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>240338</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>264254</t>
+          <t>70471</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15791; 35953</t>
+          <t>16327; 34848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9783; 29187</t>
+          <t>9937; 27782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23214; 46890</t>
+          <t>22462; 47072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15642; 35871</t>
+          <t>18318; 39782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23705; 46020</t>
+          <t>22605; 44430</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27142; 50270</t>
+          <t>25402; 50668</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65302; 99355</t>
+          <t>65930; 101316</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40732; 576943</t>
+          <t>32396; 56178</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45198; 75255</t>
+          <t>44447; 73818</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40411; 70257</t>
+          <t>39813; 69494</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95470; 136077</t>
+          <t>94094; 136655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62066; 705072</t>
+          <t>56116; 89643</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>89172</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15348; 33992</t>
+          <t>14413; 33026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27652; 53814</t>
+          <t>27146; 52274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38877; 68096</t>
+          <t>38300; 67475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24143; 53624</t>
+          <t>25006; 53677</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31991; 59902</t>
+          <t>32294; 59302</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37327; 65449</t>
+          <t>38130; 66153</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109920; 158543</t>
+          <t>111306; 157277</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35782; 59599</t>
+          <t>43362; 65228</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50764; 81536</t>
+          <t>51506; 85707</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72275; 111072</t>
+          <t>71519; 110906</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>158051; 210797</t>
+          <t>159691; 212492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68470; 104653</t>
+          <t>73514; 107108</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113122</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>179728</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>476840</t>
+          <t>301902</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73626; 110999</t>
+          <t>74179; 109749</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87233; 129412</t>
+          <t>84969; 127591</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129217; 177646</t>
+          <t>130715; 179509</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82858; 137277</t>
+          <t>101698; 148500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>132695; 182661</t>
+          <t>129995; 181669</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>150646; 204182</t>
+          <t>153299; 205236</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>351692; 431385</t>
+          <t>352922; 429414</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>161437; 979354</t>
+          <t>157768; 204755</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>217358; 277457</t>
+          <t>215957; 278037</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250421; 316364</t>
+          <t>246593; 316238</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>502869; 592778</t>
+          <t>500698; 595868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>271451; 1132535</t>
+          <t>272941; 336245</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
